--- a/output/laminas_comunales/comunal_s_isapre_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2022_valparaiso.xlsx
@@ -375,436 +375,436 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C2">
-        <v>64769</v>
+        <v>33.23652791222975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C3">
-        <v>32268</v>
+        <v>22.6613068065681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C4">
-        <v>24507</v>
+        <v>20.18400089756535</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="C5">
-        <v>17510</v>
+        <v>19.87437892565857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C6">
-        <v>17339</v>
+        <v>18.71806579890412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C7">
-        <v>10292</v>
+        <v>17.45363408521303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="C8">
-        <v>10201</v>
+        <v>16.51742103549332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C9">
-        <v>7752</v>
+        <v>14.60997941656612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C10">
-        <v>7305</v>
+        <v>14.30405827384739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C11">
-        <v>5523</v>
+        <v>12.80708492754051</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C12">
-        <v>5397</v>
+        <v>12.7504816955684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C13">
-        <v>3482</v>
+        <v>11.47286821705426</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C14">
-        <v>3454</v>
+        <v>10.33935832406781</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C15">
-        <v>3326</v>
+        <v>10.28659373570151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C16">
-        <v>3021</v>
+        <v>10.17891176147759</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C17">
-        <v>2647</v>
+        <v>10.09501187648456</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C18">
-        <v>2560</v>
+        <v>10.00205973223481</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C19">
-        <v>2473</v>
+        <v>9.980379332897318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C20">
-        <v>2428</v>
+        <v>9.92078460958129</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C21">
-        <v>2125</v>
+        <v>9.550670537812803</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="C22">
-        <v>2120</v>
+        <v>9.470516317125929</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C23">
-        <v>2029</v>
+        <v>9.262755406858645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="C24">
-        <v>1850</v>
+        <v>8.192702932026021</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="C25">
-        <v>1738</v>
+        <v>8.049892300756399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C26">
-        <v>1607</v>
+        <v>7.211752046044642</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C27">
-        <v>1443</v>
+        <v>6.500917057265132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="C28">
-        <v>1305</v>
+        <v>6.427903247360685</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C29">
-        <v>1120</v>
+        <v>6.118108166240471</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C30">
-        <v>971</v>
+        <v>5.932087822173735</v>
       </c>
     </row>
     <row r="31">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>868</v>
+        <v>5.501679660264942</v>
       </c>
     </row>
     <row r="32">
@@ -834,37 +834,37 @@
         </is>
       </c>
       <c r="C32">
-        <v>848</v>
+        <v>5.266099484568093</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C33">
-        <v>763</v>
+        <v>5.177838212552659</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C34">
-        <v>638</v>
+        <v>4.100911720552158</v>
       </c>
     </row>
     <row r="35">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>338</v>
+        <v>3.270756725372557</v>
       </c>
     </row>
     <row r="36">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>252</v>
+        <v>2.962962962962963</v>
       </c>
     </row>
     <row r="37">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>1.359003397508494</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
